--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9256770-0F63-4E93-9105-C317254B0803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20E2BFF-C80D-446E-B0C0-C59FCC44575C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="510" windowWidth="27450" windowHeight="15630" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="-90" yWindow="90" windowWidth="28800" windowHeight="17085" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -326,7 +326,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="321">
   <si>
     <t>Home</t>
   </si>
@@ -1141,30 +1141,15 @@
     <t>Over 90%</t>
   </si>
   <si>
-    <t>Liveweight grown</t>
-  </si>
-  <si>
     <t>Between 21% and 50%</t>
   </si>
   <si>
-    <t>Manure produced</t>
-  </si>
-  <si>
     <t>Regional-level data from a government or industry database/survey</t>
   </si>
   <si>
     <t>Between 51% and 90%</t>
   </si>
   <si>
-    <t>Manure sold</t>
-  </si>
-  <si>
-    <t>Percent income from liveweight sold</t>
-  </si>
-  <si>
-    <t>Percent income from manure sold</t>
-  </si>
-  <si>
     <t>Site</t>
   </si>
   <si>
@@ -1177,93 +1162,21 @@
     <t>Pasture Beef</t>
   </si>
   <si>
-    <t>Livestock production region</t>
-  </si>
-  <si>
-    <t>Cattle breed</t>
-  </si>
-  <si>
-    <t>Head count</t>
-  </si>
-  <si>
-    <t>Liveweight</t>
-  </si>
-  <si>
-    <t>Liveweight gain</t>
-  </si>
-  <si>
     <t>Less than 20%</t>
   </si>
   <si>
-    <t>Dry matter digestibility of diet</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
-    <t>Crude protein in diet</t>
-  </si>
-  <si>
-    <t>Livestock access to water bodies</t>
-  </si>
-  <si>
-    <t>Calving timing</t>
-  </si>
-  <si>
-    <t>Calving rates</t>
-  </si>
-  <si>
-    <t>Livestock sales</t>
-  </si>
-  <si>
-    <t>Livestock purchases</t>
-  </si>
-  <si>
     <t>Pasture management</t>
   </si>
   <si>
-    <t>Pasture type</t>
-  </si>
-  <si>
-    <t>Area under pasture</t>
-  </si>
-  <si>
-    <t>Pasture yield</t>
-  </si>
-  <si>
     <t>State-level data from a government or industry database/survey</t>
   </si>
   <si>
-    <t>Area of pasture renewed or removed</t>
-  </si>
-  <si>
     <t>Fertiliser applications</t>
   </si>
   <si>
-    <t>Branded inorganic fertiliser applications</t>
-  </si>
-  <si>
-    <t>Custom inorganic fertiliser blend applications</t>
-  </si>
-  <si>
-    <t>Lime applications</t>
-  </si>
-  <si>
-    <t>Organic fertiliser applications</t>
-  </si>
-  <si>
-    <t>Fuel consumption</t>
-  </si>
-  <si>
-    <t>Electricity consumption</t>
-  </si>
-  <si>
-    <t>Inbound freight use</t>
-  </si>
-  <si>
-    <t>Outbound freight use</t>
-  </si>
-  <si>
     <t>This location with spatial partitioning</t>
   </si>
   <si>
@@ -1297,22 +1210,10 @@
     <t>Data type</t>
   </si>
   <si>
-    <t>Fuel purchases</t>
-  </si>
-  <si>
-    <t>Electricity generation</t>
-  </si>
-  <si>
     <t>Fuel and electricity</t>
   </si>
   <si>
-    <t>Farm input purchases</t>
-  </si>
-  <si>
     <t>Farm input purchases, freight and waste outputs</t>
-  </si>
-  <si>
-    <t>Solid waste generation and treatment</t>
   </si>
   <si>
     <t>Total data quality score</t>
@@ -12385,7 +12286,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="94" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="D1" s="94"/>
       <c r="E1" s="94"/>
@@ -12421,7 +12322,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="80" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13013,7 +12914,7 @@
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="92" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="E28" s="93"/>
       <c r="F28" s="93"/>
@@ -13034,13 +12935,13 @@
     <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="80" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="12" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>8</v>
@@ -13089,7 +12990,7 @@
     </row>
     <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="92" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="E35" s="93"/>
       <c r="F35" s="93"/>
@@ -13110,12 +13011,12 @@
     <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="80" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="12" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>8</v>
@@ -13136,7 +13037,7 @@
     </row>
     <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E40" s="1" t="e" cm="1">
         <f t="array" ref="E40">VEERG_15_1_1_1__1_EmissionsFromPurchasedLivestock_Result_Method1</f>
@@ -13163,7 +13064,7 @@
     </row>
     <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E41" s="1" t="e" cm="1">
         <f t="array" ref="E41">VEERG_15_2_1_1__1_EmissionsFromPurchasedFeed_Result_Method1</f>
@@ -13190,7 +13091,7 @@
     </row>
     <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="E42" s="1" t="e" cm="1">
         <f t="array" ref="E42">VEERG_15_3_1_1__1_EmissionsFromPurchasedMineralSupplements_Result_Method1</f>
@@ -13217,7 +13118,7 @@
     </row>
     <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="E43" s="1" t="e" cm="1">
         <f t="array" ref="E43">VEERG_15_4_1_1__2_EmissionsFromPurchasedFertiliserComponentsVariation_Result_Method1</f>
@@ -13244,7 +13145,7 @@
     </row>
     <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="E44" s="1" t="e" cm="1">
         <f t="array" ref="E44">VEERG_15_5_1_1__1_EmissionsFromPurchasedAgrichemicals_Result_Method1</f>
@@ -13271,7 +13172,7 @@
     </row>
     <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="E45" s="1" t="e" cm="1">
         <f t="array" ref="E45">VEERG_15_6_1_1__1_EmissionsFromPurchasedLime_Result_Method1</f>
@@ -13298,7 +13199,7 @@
     </row>
     <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="E46" s="1" t="e" cm="1">
         <f t="array" ref="E46">VEERG_15_7_1_1__1_EmissionsFromPurchasedServices_Result_Method1</f>
@@ -13325,7 +13226,7 @@
     </row>
     <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="E47" s="1" t="e" cm="1">
         <f t="array" ref="E47">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_CleaningChemicals_Result_Method1</f>
@@ -13352,7 +13253,7 @@
     </row>
     <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="E48" s="1" t="e" cm="1">
         <f t="array" ref="E48">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_PharmacyChemicals_Result_Method1</f>
@@ -13379,7 +13280,7 @@
     </row>
     <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="E49" s="1" t="e" cm="1">
         <f t="array" ref="E49">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Misc_Result_Method1</f>
@@ -13406,7 +13307,7 @@
     </row>
     <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="E50" s="1" t="e" cm="1">
         <f t="array" ref="E50">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Uncategorised_Result_Method1</f>
@@ -13433,7 +13334,7 @@
     </row>
     <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="1" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="E51" s="1" t="e" cm="1">
         <f t="array" ref="E51">VEERG_15_11_1_1__1_TotalUpstreamEmissionsFromFuel_Result</f>
@@ -13488,7 +13389,7 @@
     </row>
     <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="1" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="E53" s="1" t="e" cm="1">
         <f t="array" ref="E53">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Incoming_Result_Method1</f>
@@ -13515,7 +13416,7 @@
     </row>
     <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="E54" s="1" t="e" cm="1">
         <f t="array" ref="E54">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope3_Result_Method1</f>
@@ -13542,7 +13443,7 @@
     </row>
     <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="1" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="E55" s="1" t="e" cm="1">
         <f t="array" ref="E55">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Outgoing_Result_Method1</f>
@@ -13569,7 +13470,7 @@
     </row>
     <row r="56" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="92" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="E56" s="93"/>
       <c r="F56" s="93"/>
@@ -13597,7 +13498,7 @@
     <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="92" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="E61" s="93">
         <f>SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise])</f>
@@ -13627,7 +13528,7 @@
     </row>
     <row r="67" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="90" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="E67" s="91" t="e">
         <f>Result_Enterprise_Scope1_Method1+Result_Enterprise_Scope2_Method1+Result_Enterprise_Scope3_Method1</f>
@@ -13638,12 +13539,12 @@
         <v>#NAME?</v>
       </c>
       <c r="G67" s="98" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="90" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="E68" s="91" t="e">
         <f>Result_Enterprise_Gross_Method1-Result_Enterprise_Removals</f>
@@ -13654,7 +13555,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G68" s="98" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13690,7 +13591,7 @@
   <sheetData>
     <row r="1" spans="3:18" s="94" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
       <c r="C1" s="94" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="3:18" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -13730,7 +13631,7 @@
     </row>
     <row r="36" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D36" s="78" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="E36" s="1" t="e">
         <f>Result_EmissionsForWholeProductionCycle_Method1</f>
@@ -13746,7 +13647,7 @@
     </row>
     <row r="37" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D37" s="78" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="E37" s="1" t="e">
         <f>Result_EmissionsForWholeProductionCycle_Method1-Result_CarbonRemovalsFromPlantings</f>
@@ -13788,16 +13689,16 @@
         <v>132</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>130</v>
@@ -13991,10 +13892,10 @@
         <v>132</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>174</v>
@@ -14173,10 +14074,10 @@
         <v>132</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="12"/>
@@ -15283,7 +15184,7 @@
     </row>
     <row r="37" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D37" s="2" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -15294,16 +15195,16 @@
     </row>
     <row r="42" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D42" s="21" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="G42" s="83" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="4:7" x14ac:dyDescent="0.25">
@@ -15317,7 +15218,7 @@
     </row>
     <row r="47" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D47" s="2" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -15334,7 +15235,7 @@
     </row>
     <row r="52" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D52" s="1" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="4:7" x14ac:dyDescent="0.25">
@@ -15856,7 +15757,7 @@
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D7" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E7" s="83" t="s">
         <v>247</v>
@@ -15878,14 +15779,15 @@
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D8" s="1" t="s">
-        <v>23</v>
+      <c r="D8" s="1" t="str">
+        <f>"Liveweight sold"</f>
+        <v>Liveweight sold</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>250</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>252</v>
@@ -15898,17 +15800,18 @@
       </c>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D9" s="1" t="s">
-        <v>253</v>
+      <c r="D9" s="1" t="str">
+        <f>"Liveweight grown"</f>
+        <v>Liveweight grown</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>251</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H9" s="84"/>
       <c r="I9" s="84"/>
@@ -15918,17 +15821,18 @@
       </c>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="1" t="str">
+        <f>"Manure produced"</f>
+        <v>Manure produced</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>257</v>
       </c>
       <c r="H10" s="84"/>
       <c r="I10" s="84"/>
@@ -15938,17 +15842,18 @@
       </c>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D11" s="1" t="s">
-        <v>258</v>
+      <c r="D11" s="1" t="str">
+        <f>"Manure sold"</f>
+        <v>Manure sold</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H11" s="84"/>
       <c r="I11" s="84"/>
@@ -15958,17 +15863,18 @@
       </c>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D12" s="1" t="s">
-        <v>259</v>
+      <c r="D12" s="1" t="str">
+        <f>"Percent income from liveweight sold"</f>
+        <v>Percent income from liveweight sold</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="H12" s="84"/>
       <c r="I12" s="84"/>
@@ -15978,8 +15884,9 @@
       </c>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D13" s="1" t="s">
-        <v>260</v>
+      <c r="D13" s="1" t="str">
+        <f>"Percent income from manure sold"</f>
+        <v>Percent income from manure sold</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>250</v>
@@ -16005,12 +15912,12 @@
     </row>
     <row r="16" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D18" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E18" s="83" t="s">
         <v>247</v>
@@ -16032,14 +15939,15 @@
       </c>
     </row>
     <row r="19" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D19" s="1" t="s">
-        <v>113</v>
+      <c r="D19" s="1" t="str">
+        <f>"Leaching zone"</f>
+        <v>Leaching zone</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>252</v>
@@ -16052,14 +15960,15 @@
       </c>
     </row>
     <row r="20" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D20" s="1" t="s">
-        <v>46</v>
+      <c r="D20" s="1" t="str">
+        <f>"Elevation"</f>
+        <v>Elevation</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>252</v>
@@ -16072,14 +15981,15 @@
       </c>
     </row>
     <row r="21" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D21" s="1" t="s">
-        <v>116</v>
+      <c r="D21" s="1" t="str">
+        <f>"Average temperature for reporting period"</f>
+        <v>Average temperature for reporting period</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>252</v>
@@ -16092,8 +16002,9 @@
       </c>
     </row>
     <row r="22" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D22" s="1" t="s">
-        <v>118</v>
+      <c r="D22" s="1" t="str">
+        <f>"Total rainfall for reporting period"</f>
+        <v>Total rainfall for reporting period</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>250</v>
@@ -16112,14 +16023,15 @@
       </c>
     </row>
     <row r="23" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D23" s="1" t="s">
-        <v>120</v>
+      <c r="D23" s="1" t="str">
+        <f>"Potential evapotranspiration for reporting period"</f>
+        <v>Potential evapotranspiration for reporting period</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>252</v>
@@ -16132,14 +16044,15 @@
       </c>
     </row>
     <row r="24" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D24" s="1" t="s">
-        <v>121</v>
+      <c r="D24" s="1" t="str">
+        <f>"Number of frost days for reporting period"</f>
+        <v>Number of frost days for reporting period</v>
       </c>
       <c r="E24" s="85" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F24" s="85" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G24" s="85" t="s">
         <v>252</v>
@@ -16159,12 +16072,12 @@
     </row>
     <row r="27" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D29" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E29" s="83" t="s">
         <v>247</v>
@@ -16186,14 +16099,15 @@
       </c>
     </row>
     <row r="30" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D30" s="1" t="s">
-        <v>265</v>
+      <c r="D30" s="1" t="str">
+        <f>"Livestock production region"</f>
+        <v>Livestock production region</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>250</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>252</v>
@@ -16206,8 +16120,9 @@
       </c>
     </row>
     <row r="31" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D31" s="1" t="s">
-        <v>266</v>
+      <c r="D31" s="1" t="str">
+        <f>"Cattle breed"</f>
+        <v>Cattle breed</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>250</v>
@@ -16226,8 +16141,9 @@
       </c>
     </row>
     <row r="32" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D32" s="1" t="s">
-        <v>267</v>
+      <c r="D32" s="1" t="str">
+        <f>"Head count"</f>
+        <v>Head count</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>250</v>
@@ -16236,7 +16152,7 @@
         <v>251</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H32" s="84"/>
       <c r="I32" s="84"/>
@@ -16246,8 +16162,9 @@
       </c>
     </row>
     <row r="33" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D33" s="1" t="s">
-        <v>268</v>
+      <c r="D33" s="1" t="str">
+        <f>"Liveweight"</f>
+        <v>Liveweight</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>250</v>
@@ -16256,7 +16173,7 @@
         <v>251</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H33" s="84"/>
       <c r="I33" s="84"/>
@@ -16266,8 +16183,9 @@
       </c>
     </row>
     <row r="34" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D34" s="1" t="s">
-        <v>269</v>
+      <c r="D34" s="1" t="str">
+        <f>"Liveweight gain"</f>
+        <v>Liveweight gain</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>250</v>
@@ -16276,7 +16194,7 @@
         <v>251</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H34" s="84"/>
       <c r="I34" s="84"/>
@@ -16286,17 +16204,18 @@
       </c>
     </row>
     <row r="35" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D35" s="1" t="s">
-        <v>271</v>
+      <c r="D35" s="1" t="str">
+        <f>"Dry matter digestibility of diet"</f>
+        <v>Dry matter digestibility of diet</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>250</v>
       </c>
       <c r="F35" s="85" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G35" s="85" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="H35" s="84"/>
       <c r="I35" s="84"/>
@@ -16306,17 +16225,18 @@
       </c>
     </row>
     <row r="36" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D36" s="1" t="s">
-        <v>273</v>
+      <c r="D36" s="1" t="str">
+        <f>"Crude protein in diet"</f>
+        <v>Crude protein in diet</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>250</v>
       </c>
       <c r="F36" s="85" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G36" s="85" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="H36" s="84"/>
       <c r="I36" s="84"/>
@@ -16326,8 +16246,9 @@
       </c>
     </row>
     <row r="37" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D37" s="1" t="s">
-        <v>274</v>
+      <c r="D37" s="1" t="str">
+        <f>"Livestock access to water bodies"</f>
+        <v>Livestock access to water bodies</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>250</v>
@@ -16346,8 +16267,9 @@
       </c>
     </row>
     <row r="38" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D38" s="1" t="s">
-        <v>275</v>
+      <c r="D38" s="1" t="str">
+        <f>"Calving timing"</f>
+        <v>Calving timing</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>250</v>
@@ -16356,7 +16278,7 @@
         <v>251</v>
       </c>
       <c r="G38" s="85" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H38" s="84"/>
       <c r="I38" s="84"/>
@@ -16366,8 +16288,9 @@
       </c>
     </row>
     <row r="39" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D39" s="1" t="s">
-        <v>276</v>
+      <c r="D39" s="1" t="str">
+        <f>"Calving rates"</f>
+        <v>Calving rates</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>250</v>
@@ -16376,7 +16299,7 @@
         <v>251</v>
       </c>
       <c r="G39" s="85" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H39" s="84"/>
       <c r="I39" s="84"/>
@@ -16386,8 +16309,9 @@
       </c>
     </row>
     <row r="40" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D40" s="1" t="s">
-        <v>277</v>
+      <c r="D40" s="1" t="str">
+        <f>"Livestock sales"</f>
+        <v>Livestock sales</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>250</v>
@@ -16406,8 +16330,9 @@
       </c>
     </row>
     <row r="41" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D41" s="1" t="s">
-        <v>278</v>
+      <c r="D41" s="1" t="str">
+        <f>"Livestock purchases"</f>
+        <v>Livestock purchases</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>250</v>
@@ -16433,12 +16358,12 @@
     </row>
     <row r="44" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D44" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D46" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E46" s="83" t="s">
         <v>247</v>
@@ -16460,8 +16385,9 @@
       </c>
     </row>
     <row r="47" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D47" s="1" t="s">
-        <v>280</v>
+      <c r="D47" s="1" t="str">
+        <f>"Pasture type"</f>
+        <v>Pasture type</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>250</v>
@@ -16480,8 +16406,9 @@
       </c>
     </row>
     <row r="48" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D48" s="1" t="s">
-        <v>73</v>
+      <c r="D48" s="1" t="str">
+        <f>"Irrigation method"</f>
+        <v>Irrigation method</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>250</v>
@@ -16500,8 +16427,9 @@
       </c>
     </row>
     <row r="49" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D49" s="1" t="s">
-        <v>281</v>
+      <c r="D49" s="1" t="str">
+        <f>"Area under pasture"</f>
+        <v>Area under pasture</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>250</v>
@@ -16520,17 +16448,18 @@
       </c>
     </row>
     <row r="50" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D50" s="1" t="s">
-        <v>282</v>
+      <c r="D50" s="1" t="str">
+        <f>"Pasture yield"</f>
+        <v>Pasture yield</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>250</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="H50" s="84"/>
       <c r="I50" s="84"/>
@@ -16540,8 +16469,9 @@
       </c>
     </row>
     <row r="51" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D51" s="1" t="s">
-        <v>284</v>
+      <c r="D51" s="1" t="str">
+        <f>"Area of pasture renewed or removed"</f>
+        <v>Area of pasture renewed or removed</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>250</v>
@@ -16567,12 +16497,12 @@
     </row>
     <row r="54" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D54" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D56" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E56" s="83" t="s">
         <v>247</v>
@@ -16594,8 +16524,9 @@
       </c>
     </row>
     <row r="57" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D57" s="1" t="s">
-        <v>286</v>
+      <c r="D57" s="1" t="str">
+        <f>"Branded inorganic fertiliser applications"</f>
+        <v>Branded inorganic fertiliser applications</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>250</v>
@@ -16604,7 +16535,7 @@
         <v>251</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H57" s="84"/>
       <c r="I57" s="84"/>
@@ -16614,8 +16545,9 @@
       </c>
     </row>
     <row r="58" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D58" s="1" t="s">
-        <v>287</v>
+      <c r="D58" s="1" t="str">
+        <f>"Custom inorganic fertiliser blend applications"</f>
+        <v>Custom inorganic fertiliser blend applications</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>250</v>
@@ -16634,8 +16566,9 @@
       </c>
     </row>
     <row r="59" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D59" s="1" t="s">
-        <v>288</v>
+      <c r="D59" s="1" t="str">
+        <f>"Lime applications"</f>
+        <v>Lime applications</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>250</v>
@@ -16654,8 +16587,9 @@
       </c>
     </row>
     <row r="60" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D60" s="1" t="s">
-        <v>289</v>
+      <c r="D60" s="1" t="str">
+        <f>"Organic fertiliser applications"</f>
+        <v>Organic fertiliser applications</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>250</v>
@@ -16681,12 +16615,12 @@
     </row>
     <row r="63" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D63" s="2" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D65" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E65" s="83" t="s">
         <v>247</v>
@@ -16708,8 +16642,9 @@
       </c>
     </row>
     <row r="66" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D66" s="1" t="s">
-        <v>305</v>
+      <c r="D66" s="1" t="str">
+        <f>"Fuel purchases"</f>
+        <v>Fuel purchases</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>250</v>
@@ -16718,7 +16653,7 @@
         <v>251</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H66" s="84"/>
       <c r="I66" s="84"/>
@@ -16728,8 +16663,9 @@
       </c>
     </row>
     <row r="67" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D67" s="1" t="s">
-        <v>290</v>
+      <c r="D67" s="1" t="str">
+        <f>"Fuel consumption"</f>
+        <v>Fuel consumption</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>250</v>
@@ -16748,8 +16684,9 @@
       </c>
     </row>
     <row r="68" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D68" s="1" t="s">
-        <v>291</v>
+      <c r="D68" s="1" t="str">
+        <f>"Electricity consumption"</f>
+        <v>Electricity consumption</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>250</v>
@@ -16768,8 +16705,9 @@
       </c>
     </row>
     <row r="69" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D69" s="1" t="s">
-        <v>306</v>
+      <c r="D69" s="1" t="str">
+        <f>"Electricity generation"</f>
+        <v>Electricity generation</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>250</v>
@@ -16795,12 +16733,12 @@
     </row>
     <row r="73" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D73" s="2" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D75" s="83" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="E75" s="83" t="s">
         <v>247</v>
@@ -16822,8 +16760,9 @@
       </c>
     </row>
     <row r="76" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D76" s="1" t="s">
-        <v>308</v>
+      <c r="D76" s="1" t="str">
+        <f>"Farm input purchases"</f>
+        <v>Farm input purchases</v>
       </c>
       <c r="E76" s="14" t="s">
         <v>250</v>
@@ -16832,7 +16771,7 @@
         <v>251</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H76" s="84"/>
       <c r="I76" s="84"/>
@@ -16842,8 +16781,9 @@
       </c>
     </row>
     <row r="77" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D77" s="1" t="s">
-        <v>292</v>
+      <c r="D77" s="1" t="str">
+        <f>"Inbound freight use"</f>
+        <v>Inbound freight use</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>250</v>
@@ -16862,8 +16802,9 @@
       </c>
     </row>
     <row r="78" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D78" s="1" t="s">
-        <v>293</v>
+      <c r="D78" s="1" t="str">
+        <f>"Outbound freight use"</f>
+        <v>Outbound freight use</v>
       </c>
       <c r="E78" s="14" t="s">
         <v>250</v>
@@ -16882,8 +16823,9 @@
       </c>
     </row>
     <row r="79" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D79" s="1" t="s">
-        <v>310</v>
+      <c r="D79" s="1" t="str">
+        <f>"Solid waste generation and treatment"</f>
+        <v>Solid waste generation and treatment</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>250</v>
@@ -16909,7 +16851,7 @@
     </row>
     <row r="83" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="D83" s="92" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="E83" s="93" t="str">
         <f>(J15+J26+J43+J53+J62+J71+J81)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureBeef[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FertiliserApplications[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
@@ -21075,7 +21017,7 @@
     </row>
     <row r="265" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D265" s="21" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="E265" s="21" t="s">
         <v>204</v>
@@ -21107,7 +21049,7 @@
     </row>
     <row r="267" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D267" s="21" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E267" s="21" t="s">
         <v>208</v>
@@ -21123,7 +21065,7 @@
     </row>
     <row r="268" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D268" s="21" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E268" s="21" t="s">
         <v>209</v>
@@ -21139,7 +21081,7 @@
     </row>
     <row r="269" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D269" s="21" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="E269" s="21" t="s">
         <v>211</v>
@@ -21155,7 +21097,7 @@
     </row>
     <row r="270" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D270" s="21" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="E270" s="21" t="s">
         <v>213</v>
@@ -21176,7 +21118,7 @@
     </row>
     <row r="274" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D274" s="21" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="E274" s="21" t="s">
         <v>204</v>
@@ -21192,7 +21134,7 @@
     </row>
     <row r="275" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D275" s="21" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="E275" s="21" t="s">
         <v>216</v>
@@ -21224,7 +21166,7 @@
     </row>
     <row r="277" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D277" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E277" s="21" t="s">
         <v>219</v>
@@ -21240,7 +21182,7 @@
     </row>
     <row r="278" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D278" s="21" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E278" s="21" t="s">
         <v>221</v>
@@ -21256,7 +21198,7 @@
     </row>
     <row r="279" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D279" s="21" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="E279" s="21" t="s">
         <v>223</v>
@@ -21277,7 +21219,7 @@
     </row>
     <row r="283" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D283" s="21" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="E283" s="21" t="s">
         <v>204</v>
@@ -21309,7 +21251,7 @@
     </row>
     <row r="285" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D285" s="21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E285" s="21" t="s">
         <v>228</v>
@@ -21325,7 +21267,7 @@
     </row>
     <row r="286" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D286" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E286" s="21" t="s">
         <v>230</v>
@@ -21341,7 +21283,7 @@
     </row>
     <row r="287" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D287" s="21" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E287" s="21" t="s">
         <v>231</v>
@@ -21357,7 +21299,7 @@
     </row>
     <row r="288" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D288" s="21" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="E288" s="21" t="s">
         <v>233</v>
@@ -21378,7 +21320,7 @@
     </row>
     <row r="292" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D292" s="21" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="E292" s="21" t="s">
         <v>204</v>
@@ -21394,7 +21336,7 @@
     </row>
     <row r="293" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D293" s="21" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="E293" s="21" t="s">
         <v>236</v>
@@ -21410,7 +21352,7 @@
     </row>
     <row r="294" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D294" s="21" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="E294" s="21" t="s">
         <v>238</v>
@@ -21426,7 +21368,7 @@
     </row>
     <row r="295" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D295" s="21" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="E295" s="21" t="s">
         <v>240</v>
@@ -21442,7 +21384,7 @@
     </row>
     <row r="296" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D296" s="21" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="E296" s="21" t="s">
         <v>242</v>
@@ -21458,7 +21400,7 @@
     </row>
     <row r="297" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D297" s="21" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="E297" s="21" t="s">
         <v>244</v>
@@ -21502,6 +21444,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -21696,20 +21642,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -21720,7 +21653,24 @@
 </p:properties>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21739,23 +21689,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -21764,4 +21698,12 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20E2BFF-C80D-446E-B0C0-C59FCC44575C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98074432-C277-45EF-B2F3-F826826BDBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="90" windowWidth="28800" windowHeight="17085" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2340" yWindow="1890" windowWidth="36060" windowHeight="19710" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -3896,6 +3896,17 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000073-1931-495F-914F-43EC2EA99D04}"/>
@@ -3905,6 +3916,17 @@
           <c:dPt>
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000074-1931-495F-914F-43EC2EA99D04}"/>
@@ -3914,6 +3936,17 @@
           <c:dPt>
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000075-1931-495F-914F-43EC2EA99D04}"/>
@@ -3923,6 +3956,17 @@
           <c:dPt>
             <c:idx val="3"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000076-1931-495F-914F-43EC2EA99D04}"/>
@@ -3932,6 +3976,17 @@
           <c:dPt>
             <c:idx val="4"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000077-1931-495F-914F-43EC2EA99D04}"/>
@@ -3941,6 +3996,17 @@
           <c:dPt>
             <c:idx val="5"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000078-1931-495F-914F-43EC2EA99D04}"/>
@@ -3950,6 +4016,19 @@
           <c:dPt>
             <c:idx val="6"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000079-1931-495F-914F-43EC2EA99D04}"/>
@@ -3959,6 +4038,19 @@
           <c:dPt>
             <c:idx val="7"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000007A-1931-495F-914F-43EC2EA99D04}"/>
@@ -3968,6 +4060,19 @@
           <c:dPt>
             <c:idx val="8"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000007B-1931-495F-914F-43EC2EA99D04}"/>
@@ -3977,6 +4082,19 @@
           <c:dPt>
             <c:idx val="9"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000007C-1931-495F-914F-43EC2EA99D04}"/>
@@ -3986,6 +4104,19 @@
           <c:dPt>
             <c:idx val="10"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000007D-1931-495F-914F-43EC2EA99D04}"/>
@@ -3995,6 +4126,19 @@
           <c:dPt>
             <c:idx val="11"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000007E-1931-495F-914F-43EC2EA99D04}"/>
@@ -4004,6 +4148,20 @@
           <c:dPt>
             <c:idx val="12"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{0000007F-1931-495F-914F-43EC2EA99D04}"/>
@@ -4013,6 +4171,20 @@
           <c:dPt>
             <c:idx val="13"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000080-1931-495F-914F-43EC2EA99D04}"/>
@@ -4022,6 +4194,20 @@
           <c:dPt>
             <c:idx val="14"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000081-1931-495F-914F-43EC2EA99D04}"/>
@@ -4031,6 +4217,20 @@
           <c:dPt>
             <c:idx val="15"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000082-1931-495F-914F-43EC2EA99D04}"/>
@@ -4040,6 +4240,20 @@
           <c:dPt>
             <c:idx val="16"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000083-1931-495F-914F-43EC2EA99D04}"/>
@@ -4049,6 +4263,20 @@
           <c:dPt>
             <c:idx val="17"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000084-1931-495F-914F-43EC2EA99D04}"/>
@@ -4058,6 +4286,19 @@
           <c:dPt>
             <c:idx val="18"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000085-1931-495F-914F-43EC2EA99D04}"/>
@@ -4201,760 +4442,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="1"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003A-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003C-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000003E-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000040-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000042-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000044-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000046-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000048-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="8"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004A-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="9"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004C-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="10"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000004E-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="11"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000050-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="12"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000052-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="13"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000054-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="14"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000056-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="15"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000058-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="16"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000005A-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="17"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000005C-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="18"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000005E-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="19"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000060-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="20"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000062-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="21"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000064-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="22"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000066-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="23"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000068-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="24"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000006A-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="25"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000006C-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="26"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000006E-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="27"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000070-1931-495F-914F-43EC2EA99D04}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Results - Activity period'!$D$9:$D$27</c:f>
-              <c:strCache>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>3.2.1.1-2 Enteric methane</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.2.1.1-2 Manure methane</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.2.1.3-4 Soil direct N2O</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.2.1.5-6 Soil atmospheric deposition</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.2.1.7-8 Soil leaching and runoff</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5.1.1.1-2 Inorganic fert N2O</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.1.1.3-4 Inorganic fert CO2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5.2.1.1-2 Organic fert N2O</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5.3.1.1-2 Lime CO2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.4.1.1-4 Atmos. deposition</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.5.1.1-2 Leaching &amp; runoff</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>6.2.1.1-2 Pasture residue N2O</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>6.3.1.1-2 Leach &amp; runoff (pasture)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.1.1.1-2 Transport fuel CO2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.1.1.1-2 Transport fuel CH4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>8.1.1.1-2 Transport fuel N2O</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8.2.1.1-2 Stationary fuel CO2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.2.1.1-2 Stationary fuel CH4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.2.1.1-2 Stationary fuel N2O</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Results - Activity period'!$I$9:$I$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000071-1931-495F-914F-43EC2EA99D04}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -4965,6 +4452,8 @@
           <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
+        <c:splitType val="percent"/>
+        <c:splitPos val="10"/>
         <c:secondPieSize val="75"/>
         <c:serLines>
           <c:spPr>
@@ -5223,6 +4712,8 @@
           <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
+        <c:splitType val="percent"/>
+        <c:splitPos val="10"/>
         <c:secondPieSize val="75"/>
         <c:serLines>
           <c:spPr>
@@ -13055,7 +12546,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I40" s="1" t="e">
-        <f>F40</f>
+        <f t="shared" ref="I40:I52" si="1">F40</f>
         <v>#NAME?</v>
       </c>
       <c r="J40" s="10" t="s">
@@ -13078,11 +12569,11 @@
         <v>7</v>
       </c>
       <c r="H41" s="1" t="e">
-        <f t="shared" ref="H41:H52" si="1">E41</f>
+        <f t="shared" ref="H41:H52" si="2">E41</f>
         <v>#NAME?</v>
       </c>
       <c r="I41" s="1" t="e">
-        <f t="shared" ref="I41:I52" si="2">F41</f>
+        <f t="shared" si="1"/>
         <v>#NAME?</v>
       </c>
       <c r="J41" s="10" t="s">
@@ -13105,11 +12596,11 @@
         <v>7</v>
       </c>
       <c r="H42" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I42" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I42" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J42" s="10" t="s">
@@ -13132,11 +12623,11 @@
         <v>7</v>
       </c>
       <c r="H43" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I43" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I43" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J43" s="10" t="s">
@@ -13159,11 +12650,11 @@
         <v>7</v>
       </c>
       <c r="H44" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I44" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I44" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J44" s="10" t="s">
@@ -13186,11 +12677,11 @@
         <v>7</v>
       </c>
       <c r="H45" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I45" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I45" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J45" s="10" t="s">
@@ -13213,11 +12704,11 @@
         <v>7</v>
       </c>
       <c r="H46" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I46" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I46" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J46" s="10" t="s">
@@ -13240,11 +12731,11 @@
         <v>7</v>
       </c>
       <c r="H47" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I47" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I47" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J47" s="10" t="s">
@@ -13267,11 +12758,11 @@
         <v>7</v>
       </c>
       <c r="H48" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I48" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I48" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J48" s="10" t="s">
@@ -13294,11 +12785,11 @@
         <v>7</v>
       </c>
       <c r="H49" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I49" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I49" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J49" s="10" t="s">
@@ -13321,11 +12812,11 @@
         <v>7</v>
       </c>
       <c r="H50" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I50" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I50" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J50" s="10" t="s">
@@ -13348,11 +12839,11 @@
         <v>7</v>
       </c>
       <c r="H51" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I51" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I51" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J51" s="10" t="s">
@@ -13376,11 +12867,11 @@
         <v>7</v>
       </c>
       <c r="H52" s="1" t="e">
+        <f t="shared" si="2"/>
+        <v>#NAME?</v>
+      </c>
+      <c r="I52" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>#NAME?</v>
-      </c>
-      <c r="I52" s="1" t="e">
-        <f t="shared" si="2"/>
         <v>#NAME?</v>
       </c>
       <c r="J52" s="10" t="s">
@@ -15715,7 +15206,7 @@
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="C1:M83"/>
+  <dimension ref="C1:K83"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -15727,17 +15218,18 @@
     <col min="7" max="7" width="55.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="101.28515625" style="1" customWidth="1"/>
     <col min="9" max="9" width="74.5703125" style="1" customWidth="1"/>
-    <col min="10" max="13" width="30.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="30.7109375" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:11" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
       <c r="C1" s="11" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:11" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15747,15 +15239,13 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-    </row>
-    <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="3:11" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D7" s="83" t="s">
         <v>275</v>
       </c>
@@ -15778,7 +15268,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D8" s="1" t="str">
         <f>"Liveweight sold"</f>
         <v>Liveweight sold</v>
@@ -15799,7 +15289,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="str">
         <f>"Liveweight grown"</f>
         <v>Liveweight grown</v>
@@ -15820,7 +15310,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D10" s="1" t="str">
         <f>"Manure produced"</f>
         <v>Manure produced</v>
@@ -15841,7 +15331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="str">
         <f>"Manure sold"</f>
         <v>Manure sold</v>
@@ -15862,7 +15352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D12" s="1" t="str">
         <f>"Percent income from liveweight sold"</f>
         <v>Percent income from liveweight sold</v>
@@ -15883,7 +15373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="D13" s="1" t="str">
         <f>"Percent income from manure sold"</f>
         <v>Percent income from manure sold</v>
@@ -15904,13 +15394,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
       <c r="J15" s="89">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:11" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>256</v>
       </c>
@@ -21444,10 +20934,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -21642,35 +21148,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21689,21 +21190,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98074432-C277-45EF-B2F3-F826826BDBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F744B8-BD9B-4AAA-A7C5-BF3406B1F1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1890" windowWidth="36060" windowHeight="19710" firstSheet="1" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1200" yWindow="360" windowWidth="36330" windowHeight="19485" firstSheet="1" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -215,8 +215,10 @@
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="Result_CarbonRemovalsFromPlantings">'Input - Enterprise'!$E$73</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method1">'Input - Enterprise'!$E$60</definedName>
-    <definedName name="Result_EmissionsForWholeProductionCycle_Method2">'Input - Enterprise'!$F$60</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Gross_Method1">'Input - Enterprise'!$E$60</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Gross_Method2">'Input - Enterprise'!$F$60</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Net_Method1">'Input - Enterprise'!$E$84</definedName>
+    <definedName name="Result_EmissionsForWholeProductionCycle_Net_Method2">'Input - Enterprise'!$F$84</definedName>
     <definedName name="Result_Enterprise_Gross_Method1">'Results - Activity period'!$E$67</definedName>
     <definedName name="Result_Enterprise_Gross_Method2">'Results - Activity period'!$F$67</definedName>
     <definedName name="Result_Enterprise_Net_Method1">'Results - Activity period'!$E$68</definedName>
@@ -326,7 +328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="321">
   <si>
     <t>Home</t>
   </si>
@@ -3547,7 +3549,7 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3589,7 +3591,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -11057,7 +11059,7 @@
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{AA15C232-0159-49C9-9C71-A58F1014C954}" name="Transaction name" dataCellStyle="Input text"/>
     <tableColumn id="1" xr3:uid="{307E53B0-061F-49DD-93DB-42CB4B98DC79}" name="Class (select)" dataCellStyle="Input select"/>
-    <tableColumn id="2" xr3:uid="{B15D3E20-6E9D-4B6A-BEA5-0FEB6F59B21E}" name="Sale date" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{B15D3E20-6E9D-4B6A-BEA5-0FEB6F59B21E}" name="Sale date" dataDxfId="41"/>
     <tableColumn id="3" xr3:uid="{C5AEDAD3-0B4A-4687-BC64-AC557A3FF821}" name="Head sold"/>
     <tableColumn id="4" xr3:uid="{428F255F-E5B9-46BA-8DB0-EA08A490546B}" name="Average weight per head (kg)"/>
     <tableColumn id="5" xr3:uid="{7EF1E984-68AB-4D27-831E-2DB7800A94D1}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
@@ -11324,8 +11326,8 @@
     <tableColumn id="2" xr3:uid="{68DFCF87-A6F7-4A80-91D7-A13481A1F22D}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{A40C00E6-56F7-4C78-BC6A-867F905FFAD9}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{4EEABB96-25B2-45E4-B55D-CC84B263097B}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{312AABBA-BFD5-4266-9524-F923958169B2}" name="Notes" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{11350DC8-38DD-4ED1-9576-EFE00DF98F4A}" name="Evidence files" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{312AABBA-BFD5-4266-9524-F923958169B2}" name="Notes" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{11350DC8-38DD-4ED1-9576-EFE00DF98F4A}" name="Evidence files" dataDxfId="54"/>
     <tableColumn id="7" xr3:uid="{CE5261A6-B4FC-4B62-A6AC-54C6FAAD82CB}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[When was the data sourced?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[Where is the data sourced from?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[How much of the data was from direct samples?]],#REF!,#REF!), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -11360,8 +11362,8 @@
     <tableColumn id="2" xr3:uid="{1143E7AA-62A8-44F3-B5BF-BE2379B4B905}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{828C0D88-9EF8-44A0-A6D3-0BE733D06B61}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{F8C7296B-21A2-4BA8-804A-1A97D5DE5C58}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{54570952-48C1-47E8-B45A-471C0BA7AD1C}" name="Notes" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{AB44CE99-224A-437D-A5B1-932D9C46AAB8}" name="Evidence files" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{54570952-48C1-47E8-B45A-471C0BA7AD1C}" name="Notes" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{AB44CE99-224A-437D-A5B1-932D9C46AAB8}" name="Evidence files" dataDxfId="52"/>
     <tableColumn id="7" xr3:uid="{1FE786EC-0690-4DC1-8777-E78069DC2895}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[When was the data sourced?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[Where is the data sourced from?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[How much of the data was from direct samples?]],#REF!,#REF!), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -11378,8 +11380,8 @@
     <tableColumn id="2" xr3:uid="{AC0AD7C7-1285-46C1-8760-677E5A7A447B}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{E7C35A28-6D7F-443C-BE27-871888F6021C}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{7CE87797-11C2-4242-9B92-06262C7B78FB}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{FDAFFFA7-0A46-4B10-B5C5-9C9D3BF63530}" name="Notes" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{8407DCE3-2C71-4594-89B2-6C5DC5A27F02}" name="Evidence files" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{FDAFFFA7-0A46-4B10-B5C5-9C9D3BF63530}" name="Notes" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{8407DCE3-2C71-4594-89B2-6C5DC5A27F02}" name="Evidence files" dataDxfId="50"/>
     <tableColumn id="7" xr3:uid="{55D19874-2970-424B-BFAA-72F0A3A76D94}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureBeef[[#This Row],[When was the data sourced?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureBeef[[#This Row],[Where is the data sourced from?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureBeef[[#This Row],[How much of the data was from direct samples?]],#REF!,#REF!), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -11396,8 +11398,8 @@
     <tableColumn id="2" xr3:uid="{1A35F5F3-7B50-427A-974B-341C1D9579E5}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{43931A0A-B807-40B1-9CFF-AB3981E9BF81}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{085426B4-0983-452B-ABF3-4650427E6FB2}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{540CDA6F-B045-4E43-B004-48C29A66E6C7}" name="Notes" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{4E8DFB0B-42BF-4238-AE47-4694D0ABF414}" name="Evidence files" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{540CDA6F-B045-4E43-B004-48C29A66E6C7}" name="Notes" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{4E8DFB0B-42BF-4238-AE47-4694D0ABF414}" name="Evidence files" dataDxfId="48"/>
     <tableColumn id="7" xr3:uid="{99FD6CF0-B6A4-43E3-9E7B-C0828CA99963}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[When was the data sourced?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[Where is the data sourced from?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[How much of the data was from direct samples?]],#REF!,#REF!), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -11414,8 +11416,8 @@
     <tableColumn id="2" xr3:uid="{69E55B12-88FD-4BFF-856B-A38450A42351}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{B055C1AD-6B83-432C-9F45-11C649F30314}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{BF029F0D-7D8D-4D09-A265-6DD56CC2395F}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{719E0D1E-E7A3-4744-BEE9-0CDED15EECF4}" name="Notes" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{59BA769D-6DE0-45F8-9AE4-CE630F78ADD3}" name="Evidence files" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{719E0D1E-E7A3-4744-BEE9-0CDED15EECF4}" name="Notes" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{59BA769D-6DE0-45F8-9AE4-CE630F78ADD3}" name="Evidence files" dataDxfId="46"/>
     <tableColumn id="7" xr3:uid="{AAA07962-65D6-499A-961F-5DA90E26C83A}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[When was the data sourced?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[Where is the data sourced from?]],#REF!,#REF!)+_xlfn.XLOOKUP(Table_Input_DataQuality_FertiliserApplications[[#This Row],[How much of the data was from direct samples?]],#REF!,#REF!), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -11432,8 +11434,8 @@
     <tableColumn id="2" xr3:uid="{52C64A20-79AA-4425-85FA-8095D6843A30}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{1CB192FD-80D3-400C-BB36-D4F7EF70D27C}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{3B9B8CC5-F3E8-4E1A-8F68-1416E7572F47}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{008AC1CB-FE9D-4303-9F4F-22C168CC47A0}" name="Notes" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{5014AEED-6FC3-4D88-9D37-146835135CBE}" name="Evidence files" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{008AC1CB-FE9D-4303-9F4F-22C168CC47A0}" name="Notes" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{5014AEED-6FC3-4D88-9D37-146835135CBE}" name="Evidence files" dataDxfId="44"/>
     <tableColumn id="7" xr3:uid="{1B5A6979-2182-4CA3-8C33-274D46A3229F}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -11443,15 +11445,15 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B673E621-7DB1-4295-9961-C61CC800B135}" name="Table_Input_DataQuality_FarmInputsFreightWaste" displayName="Table_Input_DataQuality_FarmInputsFreightWaste" ref="D75:J79" totalsRowShown="0" headerRowCellStyle="Input table column header">
-  <autoFilter ref="D75:J79" xr:uid="{B673E621-7DB1-4295-9961-C61CC800B135}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B673E621-7DB1-4295-9961-C61CC800B135}" name="Table_Input_DataQuality_FarmInputsFreightWaste" displayName="Table_Input_DataQuality_FarmInputsFreightWaste" ref="D75:J80" totalsRowShown="0" headerRowCellStyle="Input table column header">
+  <autoFilter ref="D75:J80" xr:uid="{B673E621-7DB1-4295-9961-C61CC800B135}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{25477CEA-09D1-4F2E-858D-E5B2B52CA880}" name="Data type" dataCellStyle="Content normal"/>
     <tableColumn id="2" xr3:uid="{8C7E7881-1860-4180-B538-825A80D47FF5}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{27F48332-E1B6-4C4D-BBAA-CBFB23977161}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{BBFCE3B0-5D6C-410D-9626-0A3427B2279C}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{6F18E8CD-2E03-497F-AEA7-2F9200F34478}" name="Notes" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{A8148FCB-F76E-4E6E-A140-C2F5CA96A211}" name="Evidence files" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{6F18E8CD-2E03-497F-AEA7-2F9200F34478}" name="Notes" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{A8148FCB-F76E-4E6E-A140-C2F5CA96A211}" name="Evidence files" dataDxfId="42"/>
     <tableColumn id="7" xr3:uid="{80B2DAE6-FCD5-49CC-8620-FFFC3957CF38}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -13125,11 +13127,11 @@
         <v>289</v>
       </c>
       <c r="E36" s="1" t="e">
-        <f>Result_EmissionsForWholeProductionCycle_Method1</f>
+        <f>Result_EmissionsForWholeProductionCycle_Gross_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F36" s="1" t="e">
-        <f>Result_EmissionsForWholeProductionCycle_Method2</f>
+        <f>Result_EmissionsForWholeProductionCycle_Gross_Method2</f>
         <v>#NAME?</v>
       </c>
       <c r="G36" s="10" t="s">
@@ -13141,11 +13143,11 @@
         <v>281</v>
       </c>
       <c r="E37" s="1" t="e">
-        <f>Result_EmissionsForWholeProductionCycle_Method1-Result_CarbonRemovalsFromPlantings</f>
+        <f>Result_EmissionsForWholeProductionCycle_Net_Method1</f>
         <v>#NAME?</v>
       </c>
       <c r="F37" s="1" t="e">
-        <f>Result_EmissionsForWholeProductionCycle_Method2-Result_CarbonRemovalsFromPlantings</f>
+        <f>Result_EmissionsForWholeProductionCycle_Net_Method2</f>
         <v>#NAME?</v>
       </c>
       <c r="G37" s="10" t="s">
@@ -13225,11 +13227,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="J44" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F44)*H44</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method1/F44)*H44</f>
         <v>#NAME?</v>
       </c>
       <c r="K44" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/G44)*I44</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method2/G44)*I44</f>
         <v>#NAME?</v>
       </c>
       <c r="L44" s="10" t="s">
@@ -13295,11 +13297,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="J46" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F46)*H46</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method1/F46)*H46</f>
         <v>#NAME?</v>
       </c>
       <c r="K46" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/G46)*I46</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method2/G46)*I46</f>
         <v>#NAME?</v>
       </c>
       <c r="L46" s="10" t="s">
@@ -13422,11 +13424,11 @@
         <v>0.8</v>
       </c>
       <c r="J52" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F52)*H52</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method1/F52)*H52</f>
         <v>#NAME?</v>
       </c>
       <c r="K52" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/G52)*H52</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method2/G52)*H52</f>
         <v>#NAME?</v>
       </c>
       <c r="L52" s="10" t="s">
@@ -13484,11 +13486,11 @@
         <v>0.2</v>
       </c>
       <c r="J54" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method1/F54)*H54</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method1/F54)*H54</f>
         <v>#NAME?</v>
       </c>
       <c r="K54" s="1" t="e">
-        <f>(Result_EmissionsForWholeProductionCycle_Method2/G54)*H54</f>
+        <f>(Result_EmissionsForWholeProductionCycle_Gross_Method2/G54)*H54</f>
         <v>#NAME?</v>
       </c>
       <c r="L54" s="10" t="s">
@@ -14392,7 +14394,7 @@
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="C1:J73"/>
+  <dimension ref="C1:J84"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -14831,13 +14833,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="4:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D65" s="80" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2023 and 31 March 2025</v>
       </c>
     </row>
-    <row r="67" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D67" s="83" t="s">
         <v>125</v>
       </c>
@@ -14846,7 +14848,7 @@
       </c>
       <c r="F67" s="83"/>
     </row>
-    <row r="68" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D68" s="1" t="str" cm="1">
         <f t="array" ref="D68:D70">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
@@ -14859,7 +14861,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="69" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D69" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
@@ -14871,7 +14873,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D70" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
@@ -14883,7 +14885,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E71" s="77">
         <f>IF(ISBLANK($D71), 0, IF(ISNUMBER(SEARCH("reporting", $D71)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -14892,7 +14894,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="72" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E72" s="77">
         <f>IF(ISBLANK($D72), 0, IF(ISNUMBER(SEARCH("reporting", $D72)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -14901,7 +14903,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D73" s="95" t="s">
         <v>141</v>
       </c>
@@ -14911,6 +14913,114 @@
       </c>
       <c r="F73" s="96" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="76" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D76" s="80" t="str">
+        <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
+        <v>Net emissions from other activity periods in the production timeframe 1 November 2023 to 31 March 2025</v>
+      </c>
+    </row>
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D78" s="83" t="s">
+        <v>125</v>
+      </c>
+      <c r="E78" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D79" s="1" t="str" cm="1">
+        <f t="array" ref="D79:D81">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
+        <v>01 Jan 2023 to 31 Dec 2023</v>
+      </c>
+      <c r="E79" s="77" t="str">
+        <f>IF(ISBLANK($D79), 0, IF(ISNUMBER(SEARCH("reporting", $D79)), E55-$E$68, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="F79" s="77" t="str">
+        <f>IF(ISBLANK($D79), 0, IF(ISNUMBER(SEARCH("reporting", $D79)), F55-$E$68, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D80" s="1" t="str">
+        <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
+      </c>
+      <c r="E80" s="77" t="e">
+        <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$69, "Enter value"))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F80" s="77" t="e">
+        <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), F56-$E$69, "Enter value"))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D81" s="1" t="str">
+        <v>01 Jan 2025 to 31 Dec 2025</v>
+      </c>
+      <c r="E81" s="77" t="str">
+        <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$70, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="F81" s="77" t="str">
+        <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), F57-$E$70, "Enter value"))</f>
+        <v>Enter value</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E82" s="77">
+        <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$71, "Enter value"))</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="77">
+        <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), F58-$E$71, "Enter value"))</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="E83" s="77">
+        <f>IF(ISBLANK($D83), 0, IF(ISNUMBER(SEARCH("reporting", $D83)), E59-$E$72, "Enter value"))</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="77">
+        <f>IF(ISBLANK($D83), 0, IF(ISNUMBER(SEARCH("reporting", $D83)), F59-$E$72, "Enter value"))</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D84" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="E84" s="89" t="e">
+        <f>SUM(E79:E83)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F84" s="89" t="e">
+        <f>SUM(F79:F83)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="G84" s="96" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15206,7 +15316,7 @@
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="C1:K83"/>
+  <dimension ref="C1:K84"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -16314,49 +16424,64 @@
     </row>
     <row r="79" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D79" s="1" t="str">
-        <f>"Solid waste generation and treatment"</f>
-        <v>Solid waste generation and treatment</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="F79" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="G79" s="14" t="s">
-        <v>252</v>
-      </c>
+        <f>"Use of contractors and service providers"</f>
+        <v>Use of contractors and service providers</v>
+      </c>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
       <c r="H79" s="84"/>
       <c r="I79" s="84"/>
       <c r="J79" s="16">
         <f>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D80" s="1" t="str">
+        <f>"Solid waste generation and treatment"</f>
+        <v>Solid waste generation and treatment</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="H80" s="84"/>
+      <c r="I80" s="84"/>
+      <c r="J80" s="16">
+        <f>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="J81" s="89">
+    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="J82" s="89">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="83" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="D83" s="92" t="s">
+    <row r="84" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="D84" s="92" t="s">
         <v>278</v>
       </c>
-      <c r="E83" s="93" t="str">
-        <f>(J15+J26+J43+J53+J62+J71+J81)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureBeef[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FertiliserApplications[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
-        <v>511 out of 615</v>
+      <c r="E84" s="93" t="str">
+        <f>(J15+J26+J43+J53+J62+J71+J82)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureBeef[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FertiliserApplications[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
+        <v>511 out of 630</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F13 F19:F24 F30:F41 F47:F51 F57:F60 F66:F69 F76:F79" xr:uid="{7A41F482-9DC2-427F-BD67-9E7030E9FA1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F13 F19:F24 F30:F41 F47:F51 F57:F60 F66:F69 F76:F80" xr:uid="{7A41F482-9DC2-427F-BD67-9E7030E9FA1D}">
       <formula1>INDIRECT("Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E13 E19:E24 E30:E41 E47:E51 E57:E60 E66:E69 E76:E79" xr:uid="{A2F79B94-E5F1-44B9-A20F-B6166F7EA291}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E13 E19:E24 E30:E41 E47:E51 E57:E60 E66:E69 E76:E80" xr:uid="{A2F79B94-E5F1-44B9-A20F-B6166F7EA291}">
       <formula1>INDIRECT("Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G13 G19:G24 G30:G41 G47:G51 G57:G60 G66:G69 G76:G79" xr:uid="{BA67DDE5-AE35-4EC9-9563-5791102272E4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G13 G19:G24 G30:G41 G47:G51 G57:G60 G66:G69 G76:G80" xr:uid="{BA67DDE5-AE35-4EC9-9563-5791102272E4}">
       <formula1>INDIRECT("Table_SourceData_DataQuality_SampleSize[User friendly description]")</formula1>
     </dataValidation>
   </dataValidations>
@@ -20934,6 +21059,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -20942,7 +21071,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -20953,7 +21082,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -21148,11 +21277,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -21160,7 +21293,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -21171,7 +21304,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21188,12 +21321,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_PastureBeef_Template_WIP_v01.xlsx
@@ -641,9 +641,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -651,9 +651,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -662,9 +662,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -672,9 +672,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -698,9 +698,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -708,9 +708,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -1363,108 +1363,106 @@
   </numFmts>
   <fonts count="55" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1475,219 +1473,217 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -1695,34 +1691,34 @@
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF0C769E"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2575,11 +2571,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2599,11 +2594,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2623,11 +2617,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2647,11 +2640,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2671,11 +2663,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2695,11 +2686,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2719,11 +2709,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2743,11 +2732,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2767,11 +2755,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2791,11 +2778,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2815,11 +2801,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2839,11 +2824,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2863,11 +2847,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2887,11 +2870,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2911,11 +2893,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2935,11 +2916,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2959,11 +2939,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2983,11 +2962,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3007,11 +2985,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3031,11 +3008,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3055,11 +3031,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3079,11 +3054,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3103,11 +3077,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3127,11 +3100,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3151,11 +3123,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3175,11 +3146,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3199,11 +3169,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3223,11 +3192,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3247,11 +3215,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3271,11 +3238,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3295,11 +3261,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3319,11 +3284,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3343,11 +3307,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3367,11 +3330,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3391,11 +3353,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3415,11 +3376,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3439,11 +3399,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3463,11 +3422,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3487,11 +3445,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3511,11 +3468,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3535,11 +3491,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3858,7 +3813,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4548,7 +4503,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4926,17 +4881,17 @@
         <a:lstStyle/>
         <a:p>
           <a:fld id="{BE25C2B2-0BD3-425F-A499-8DEB98E49F87}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -5003,24 +4958,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{E1CF640B-5306-48D2-B952-88A44FBEE044}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5084,24 +5039,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A12C616B-A256-4412-8E07-9A9AFDDE19C8}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5165,24 +5120,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A85D4D86-42B2-4B88-81D8-F406E4392F0C}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5246,24 +5201,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{12CB6A43-519A-4BE9-9BAA-F4B8A2722440}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5327,24 +5282,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{BFB47873-57C9-4A6B-8346-5DDEF9E8D242}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5407,16 +5362,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -5482,36 +5437,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -5577,18 +5532,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -5656,7 +5611,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -5774,16 +5729,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -5849,36 +5804,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -5944,18 +5899,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6123,16 +6078,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -6198,36 +6153,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -6293,18 +6248,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6366,7 +6321,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -6390,7 +6345,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6458,7 +6413,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -6581,16 +6536,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -6656,36 +6611,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -6751,18 +6706,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6934,7 +6889,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -6958,7 +6913,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7020,7 +6975,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7044,7 +6999,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7106,7 +7061,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7130,7 +7085,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7192,7 +7147,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7216,7 +7171,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7278,7 +7233,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7302,7 +7257,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7364,7 +7319,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7388,7 +7343,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7450,7 +7405,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7474,7 +7429,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7543,24 +7498,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{8B8ADE77-8739-4C42-8C9D-E087028DA258}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7624,24 +7579,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{F9A87D5F-A637-4BA0-BFE4-996CA0B467D5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7705,24 +7660,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{1924562D-F9FD-4007-A893-9658B36EA5E8}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7786,24 +7741,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9178CED4-C7B4-4572-B5FF-C2C28E3FD695}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7867,24 +7822,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{47E4CB1C-EDB4-4181-B8C4-5B02C43CACE3}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7948,24 +7903,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{52E2C27E-76F6-4365-A748-3D63EC144A1C}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8029,24 +7984,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{7ECA65A0-CBD7-46CD-8C95-E7E852DDA32D}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8110,24 +8065,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{76248843-A903-4882-925A-19F5BC60ACE3}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8190,16 +8145,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -8265,36 +8220,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -8360,18 +8315,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8439,7 +8394,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -8557,16 +8512,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -8632,36 +8587,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -8727,18 +8682,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8906,16 +8861,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -8981,36 +8936,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -9076,18 +9031,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9149,7 +9104,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -9173,7 +9128,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9241,7 +9196,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -9364,16 +9319,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -9439,36 +9394,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -9534,18 +9489,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9717,7 +9672,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -9741,7 +9696,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9803,7 +9758,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -9827,7 +9782,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9889,7 +9844,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -9913,7 +9868,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9975,7 +9930,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -9999,7 +9954,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10061,7 +10016,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10085,7 +10040,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10147,7 +10102,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10171,7 +10126,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10233,7 +10188,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10257,7 +10212,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10326,24 +10281,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{CB7BF3CE-0316-4BA7-A0BD-943D37538344}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -10407,24 +10362,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{50191ECC-A3E9-4A88-BA70-A94CDD98CFD4}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -10487,7 +10442,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Liveweight sold</a:t>
           </a:r>
         </a:p>
@@ -10619,7 +10574,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Manure sold</a:t>
           </a:r>
         </a:p>
@@ -11505,12 +11460,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -11721,31 +11676,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="86" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="87" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -11763,7 +11718,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K75"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -11790,14 +11745,14 @@
       <c r="J1" s="94"/>
       <c r="K1" s="94"/>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -11807,10 +11762,10 @@
         <v>Emissions breakdown for activities running between 1 January 2024 and 31 December 2024</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -11818,13 +11773,13 @@
         <v>297</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -11849,7 +11804,7 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>147</v>
@@ -11877,7 +11832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -11907,7 +11862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -11938,7 +11893,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -11969,7 +11924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -12000,7 +11955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -12031,7 +11986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>149</v>
@@ -12059,7 +12014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -12089,7 +12044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -12120,7 +12075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -12151,7 +12106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -12182,7 +12137,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12213,7 +12168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="s">
         <v>155</v>
       </c>
@@ -12240,7 +12195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>156</v>
@@ -12268,7 +12223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="D23" s="1" t="s">
         <v>158</v>
@@ -12296,7 +12251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="D24" s="1" t="s">
         <v>157</v>
@@ -12324,7 +12279,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>159</v>
       </c>
@@ -12351,7 +12306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
         <v>160</v>
       </c>
@@ -12378,7 +12333,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
         <v>161</v>
       </c>
@@ -12405,7 +12360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="92" t="s">
         <v>293</v>
       </c>
@@ -12424,15 +12379,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="80" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="12" t="s">
         <v>295</v>
       </c>
@@ -12453,7 +12408,7 @@
       </c>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="e" cm="1">
         <f t="array" ref="D34">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -12481,7 +12436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="92" t="s">
         <v>296</v>
       </c>
@@ -12500,14 +12455,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="80" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="12" t="s">
         <v>299</v>
       </c>
@@ -12528,7 +12483,7 @@
       </c>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
         <v>300</v>
       </c>
@@ -12555,7 +12510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
         <v>301</v>
       </c>
@@ -12582,7 +12537,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
         <v>302</v>
       </c>
@@ -12609,7 +12564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
         <v>303</v>
       </c>
@@ -12636,7 +12591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
         <v>304</v>
       </c>
@@ -12663,7 +12618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
         <v>305</v>
       </c>
@@ -12690,7 +12645,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
         <v>306</v>
       </c>
@@ -12717,7 +12672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="s">
         <v>307</v>
       </c>
@@ -12744,7 +12699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
         <v>308</v>
       </c>
@@ -12771,7 +12726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
         <v>309</v>
       </c>
@@ -12798,7 +12753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="s">
         <v>310</v>
       </c>
@@ -12825,7 +12780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="1" t="s">
         <v>311</v>
       </c>
@@ -12852,7 +12807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="1" t="e" cm="1">
         <f t="array" ref="D52">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -12880,7 +12835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="1" t="s">
         <v>312</v>
       </c>
@@ -12907,7 +12862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
         <v>313</v>
       </c>
@@ -12934,7 +12889,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="1" t="s">
         <v>314</v>
       </c>
@@ -12961,7 +12916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="92" t="s">
         <v>315</v>
       </c>
@@ -12980,16 +12935,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="80" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2024 and 31 December 2024</v>
       </c>
     </row>
-    <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="92" t="s">
         <v>290</v>
       </c>
@@ -13001,16 +12956,16 @@
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="80" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2024 and 31 December 2024</v>
       </c>
     </row>
-    <row r="65" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="12"/>
       <c r="E66" s="12" t="s">
         <v>142</v>
@@ -13019,7 +12974,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="67" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="90" t="s">
         <v>320</v>
       </c>
@@ -13035,7 +12990,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="68" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="90" t="s">
         <v>291</v>
       </c>
@@ -13051,13 +13006,13 @@
         <v>292</v>
       </c>
     </row>
-    <row r="69" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13071,7 +13026,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="C1:R60"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -13082,13 +13037,13 @@
     <col min="14" max="18" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:18" s="94" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:18" s="94" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="94" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="3:18" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:18" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:18" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C3" s="99"/>
       <c r="D3" s="99"/>
       <c r="E3" s="99"/>
@@ -13106,13 +13061,13 @@
       <c r="Q3" s="99"/>
       <c r="R3" s="99"/>
     </row>
-    <row r="32" spans="4:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2023 and 31 March 2025</v>
       </c>
     </row>
-    <row r="35" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
         <v>142</v>
@@ -13122,7 +13077,7 @@
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="78" t="s">
         <v>289</v>
       </c>
@@ -13138,7 +13093,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="78" t="s">
         <v>281</v>
       </c>
@@ -13154,7 +13109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D39" s="89"/>
       <c r="E39" s="89"/>
       <c r="F39" s="89"/>
@@ -13163,18 +13118,18 @@
       <c r="I39" s="89"/>
       <c r="J39" s="89"/>
     </row>
-    <row r="40" spans="4:12" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D40" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2023 and 31 March 2025</v>
       </c>
     </row>
-    <row r="42" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D42" s="80" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="43" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="12" t="s">
         <v>145</v>
       </c>
@@ -13203,7 +13158,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="s">
         <v>176</v>
       </c>
@@ -13238,7 +13193,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="45" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="s">
         <v>177</v>
       </c>
@@ -13273,7 +13228,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>178</v>
       </c>
@@ -13308,7 +13263,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="47" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="s">
         <v>179</v>
       </c>
@@ -13343,7 +13298,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="s">
         <v>135</v>
       </c>
@@ -13372,12 +13327,12 @@
       </c>
       <c r="L48" s="10"/>
     </row>
-    <row r="50" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D50" s="80" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="51" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="12" t="s">
         <v>145</v>
       </c>
@@ -13404,7 +13359,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="1" t="s">
         <v>176</v>
       </c>
@@ -13435,7 +13390,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="s">
         <v>177</v>
       </c>
@@ -13466,7 +13421,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="54" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="s">
         <v>178</v>
       </c>
@@ -13497,7 +13452,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="s">
         <v>179</v>
       </c>
@@ -13528,7 +13483,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="s">
         <v>135</v>
       </c>
@@ -13554,12 +13509,12 @@
       </c>
       <c r="L56" s="10"/>
     </row>
-    <row r="58" spans="4:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:12" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D58" s="80" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="12" t="s">
         <v>145</v>
       </c>
@@ -13584,7 +13539,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="60" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:12" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D60" s="1" t="s">
         <v>144</v>
       </c>
@@ -13624,7 +13579,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="23" customWidth="1"/>
@@ -13645,7 +13600,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -13656,7 +13611,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13683,7 +13638,7 @@
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -13698,19 +13653,19 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>105</v>
       </c>
       <c r="N5" s="32"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -13722,7 +13677,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="46"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -13734,14 +13689,14 @@
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="50"/>
       <c r="F9" s="17"/>
       <c r="N9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -13756,7 +13711,7 @@
       </c>
       <c r="N10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -13773,7 +13728,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="41"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -13788,7 +13743,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -13805,7 +13760,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -13822,7 +13777,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>118</v>
@@ -13836,7 +13791,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -13852,7 +13807,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -13867,7 +13822,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -13881,7 +13836,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13896,7 +13851,7 @@
       <c r="G19" s="51"/>
       <c r="N19" s="32"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13912,7 +13867,7 @@
       <c r="G20" s="50"/>
       <c r="N20" s="34"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>124</v>
@@ -13924,7 +13879,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>78</v>
@@ -13935,29 +13890,29 @@
       </c>
       <c r="G22" s="54"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="34"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="L30" s="52"/>
       <c r="M30" s="52"/>
@@ -13974,7 +13929,7 @@
       <c r="X30" s="52"/>
       <c r="Y30" s="52"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="L31" s="53"/>
       <c r="M31" s="53"/>
@@ -13991,7 +13946,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="53"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="L32" s="53"/>
       <c r="M32" s="53"/>
@@ -14008,7 +13963,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="53"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="L33" s="53"/>
       <c r="M33" s="53"/>
@@ -14025,7 +13980,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="53"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="55"/>
       <c r="K34" s="56"/>
@@ -14044,7 +13999,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="53"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="55"/>
       <c r="K35" s="56"/>
@@ -14063,7 +14018,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="53"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="57"/>
       <c r="E36" s="57"/>
@@ -14088,7 +14043,7 @@
       <c r="X36" s="53"/>
       <c r="Y36" s="53"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="57"/>
       <c r="E37" s="57"/>
@@ -14113,7 +14068,7 @@
       <c r="X37" s="53"/>
       <c r="Y37" s="53"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="57"/>
       <c r="E38" s="57"/>
@@ -14138,7 +14093,7 @@
       <c r="X38" s="53"/>
       <c r="Y38" s="53"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="57"/>
       <c r="E39" s="57"/>
@@ -14163,7 +14118,7 @@
       <c r="X39" s="53"/>
       <c r="Y39" s="53"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
@@ -14188,104 +14143,104 @@
       <c r="X40" s="63"/>
       <c r="Y40" s="63"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="64"/>
       <c r="E47" s="64"/>
       <c r="F47" s="64"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="65"/>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="66"/>
       <c r="G49" s="66"/>
       <c r="H49" s="65"/>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="65"/>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="67"/>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
       <c r="G51" s="68"/>
       <c r="H51" s="69"/>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="70"/>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="71"/>
       <c r="F57" s="72"/>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
       <c r="E58" s="73"/>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
       <c r="E59" s="73"/>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
       <c r="E60" s="74"/>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="71"/>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="73"/>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="73"/>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="74"/>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
@@ -14293,7 +14248,7 @@
       <c r="H69" s="75"/>
       <c r="I69" s="75"/>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
@@ -14301,7 +14256,7 @@
       <c r="H70" s="75"/>
       <c r="I70" s="75"/>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
@@ -14309,7 +14264,7 @@
       <c r="H71" s="75"/>
       <c r="I71" s="75"/>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
@@ -14317,59 +14272,59 @@
       <c r="H72" s="75"/>
       <c r="I72" s="75"/>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="76"/>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="76"/>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="76"/>
     </row>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="76"/>
     </row>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="76"/>
     </row>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -14395,7 +14350,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J84"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14409,7 +14364,7 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="29" t="s">
         <v>162</v>
       </c>
@@ -14421,7 +14376,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -14431,7 +14386,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -14441,7 +14396,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>97</v>
       </c>
@@ -14449,13 +14404,13 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="33"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>98</v>
       </c>
@@ -14465,7 +14420,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="13" t="s">
         <v>100</v>
       </c>
@@ -14475,13 +14430,13 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="37" t="s">
         <v>102</v>
       </c>
@@ -14489,13 +14444,13 @@
       <c r="F10" s="39"/>
       <c r="G10" s="40"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="13" t="s">
         <v>20</v>
       </c>
@@ -14507,7 +14462,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="13" t="s">
         <v>21</v>
       </c>
@@ -14520,16 +14475,16 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
-    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
@@ -14540,7 +14495,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="s">
         <v>18</v>
       </c>
@@ -14551,7 +14506,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="s">
         <v>19</v>
       </c>
@@ -14563,7 +14518,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="s">
         <v>23</v>
       </c>
@@ -14575,7 +14530,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="s">
         <v>24</v>
       </c>
@@ -14586,7 +14541,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="s">
         <v>25</v>
       </c>
@@ -14597,7 +14552,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="s">
         <v>164</v>
       </c>
@@ -14608,7 +14563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D26" s="1" t="s">
         <v>165</v>
       </c>
@@ -14619,7 +14574,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D27" s="1" t="s">
         <v>26</v>
       </c>
@@ -14630,7 +14585,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="1" t="s">
         <v>27</v>
       </c>
@@ -14641,7 +14596,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="1" t="s">
         <v>28</v>
       </c>
@@ -14653,7 +14608,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="s">
         <v>166</v>
       </c>
@@ -14664,7 +14619,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="s">
         <v>167</v>
       </c>
@@ -14675,18 +14630,18 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D37" s="2" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="40" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D40" s="80" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2024 to 31, December, 2024 from environmental plantings</v>
       </c>
     </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="21" t="s">
         <v>282</v>
       </c>
@@ -14700,7 +14655,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="43" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="35"/>
       <c r="E43" s="77"/>
       <c r="F43" s="19"/>
@@ -14709,29 +14664,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D47" s="2" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="49" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D49" s="80" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2023 to 31 March 2025</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="81" t="str" cm="1">
         <f t="array" ref="D51">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 3 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="52" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="83" t="s">
         <v>125</v>
       </c>
@@ -14742,7 +14697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="str" cm="1">
         <f t="array" ref="D55:D57">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
@@ -14759,7 +14714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
@@ -14775,7 +14730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
@@ -14791,7 +14746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E58" s="77">
         <f>IF(ISBLANK($D58), 0, IF(ISNUMBER(SEARCH("reporting", $D58)), Result_Enterprise_Scope1_Method1, "Enter value"))</f>
         <v>0</v>
@@ -14804,7 +14759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E59" s="77">
         <f>IF(ISBLANK($D59), 0, IF(ISNUMBER(SEARCH("reporting", $D59)), Result_Enterprise_Scope1_Method1, "Enter value"))</f>
         <v>0</v>
@@ -14817,7 +14772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D60" s="95" t="s">
         <v>140</v>
       </c>
@@ -14833,13 +14788,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D65" s="80" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2023 and 31 March 2025</v>
       </c>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="83" t="s">
         <v>125</v>
       </c>
@@ -14848,7 +14803,7 @@
       </c>
       <c r="F67" s="83"/>
     </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D68" s="1" t="str" cm="1">
         <f t="array" ref="D68:D70">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
@@ -14861,7 +14816,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D69" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
@@ -14873,7 +14828,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D70" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
@@ -14885,7 +14840,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E71" s="77">
         <f>IF(ISBLANK($D71), 0, IF(ISNUMBER(SEARCH("reporting", $D71)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -14894,7 +14849,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E72" s="77">
         <f>IF(ISBLANK($D72), 0, IF(ISNUMBER(SEARCH("reporting", $D72)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -14903,7 +14858,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D73" s="95" t="s">
         <v>141</v>
       </c>
@@ -14915,13 +14870,13 @@
         <v>139</v>
       </c>
     </row>
-    <row r="76" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D76" s="80" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2023 to 31 March 2025</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="83" t="s">
         <v>125</v>
       </c>
@@ -14932,7 +14887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D79" s="1" t="str" cm="1">
         <f t="array" ref="D79:D81">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2023 to 31 Dec 2023</v>
@@ -14949,7 +14904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D80" s="1" t="str">
         <v>01 Jan 2024 to 31 Dec 2024 (This reporting cycle)</v>
       </c>
@@ -14965,7 +14920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D81" s="1" t="str">
         <v>01 Jan 2025 to 31 Dec 2025</v>
       </c>
@@ -14981,7 +14936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E82" s="77">
         <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$71, "Enter value"))</f>
         <v>0</v>
@@ -14994,7 +14949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E83" s="77">
         <f>IF(ISBLANK($D83), 0, IF(ISNUMBER(SEARCH("reporting", $D83)), E59-$E$72, "Enter value"))</f>
         <v>0</v>
@@ -15007,7 +14962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D84" s="95" t="s">
         <v>140</v>
       </c>
@@ -15037,7 +14992,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15046,7 +15001,7 @@
     <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -15054,8 +15009,8 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15066,7 +15021,7 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D5" s="71" t="s">
         <v>185</v>
       </c>
@@ -15074,10 +15029,10 @@
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>181</v>
       </c>
@@ -15086,7 +15041,7 @@
       </c>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="s">
         <v>182</v>
       </c>
@@ -15095,7 +15050,7 @@
       </c>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="s">
         <v>73</v>
       </c>
@@ -15104,7 +15059,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="s">
         <v>183</v>
       </c>
@@ -15124,7 +15079,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15133,7 +15088,7 @@
     <col min="13" max="13" width="4.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -15141,8 +15096,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15155,12 +15110,12 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D5" s="81" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="21" t="s">
         <v>188</v>
       </c>
@@ -15180,7 +15135,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="35"/>
       <c r="E7" s="14" t="s">
         <v>194</v>
@@ -15199,7 +15154,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="35"/>
       <c r="E8" s="14"/>
       <c r="F8" s="82"/>
@@ -15210,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="35"/>
       <c r="E9" s="14"/>
       <c r="F9" s="82"/>
@@ -15221,7 +15176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="35"/>
       <c r="E10" s="14"/>
       <c r="F10" s="82"/>
@@ -15232,7 +15187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="35"/>
       <c r="E11" s="14"/>
       <c r="F11" s="82"/>
@@ -15243,7 +15198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="35"/>
       <c r="E12" s="14"/>
       <c r="F12" s="82"/>
@@ -15254,7 +15209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="35"/>
       <c r="E13" s="14"/>
       <c r="F13" s="82"/>
@@ -15265,7 +15220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D14" s="35"/>
       <c r="E14" s="14"/>
       <c r="F14" s="82"/>
@@ -15276,7 +15231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D15" s="35"/>
       <c r="E15" s="14"/>
       <c r="F15" s="82"/>
@@ -15287,7 +15242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D16" s="35"/>
       <c r="E16" s="14"/>
       <c r="F16" s="82"/>
@@ -15317,7 +15272,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:K84"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15333,13 +15288,13 @@
     <col min="12" max="12" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="11" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="3:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:11" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:11" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15350,12 +15305,12 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="5" spans="3:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="83" t="s">
         <v>275</v>
       </c>
@@ -15378,7 +15333,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="str">
         <f>"Liveweight sold"</f>
         <v>Liveweight sold</v>
@@ -15399,7 +15354,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="str">
         <f>"Liveweight grown"</f>
         <v>Liveweight grown</v>
@@ -15420,7 +15375,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="str">
         <f>"Manure produced"</f>
         <v>Manure produced</v>
@@ -15441,7 +15396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="1" t="str">
         <f>"Manure sold"</f>
         <v>Manure sold</v>
@@ -15462,7 +15417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="1" t="str">
         <f>"Percent income from liveweight sold"</f>
         <v>Percent income from liveweight sold</v>
@@ -15483,7 +15438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="1" t="str">
         <f>"Percent income from manure sold"</f>
         <v>Percent income from manure sold</v>
@@ -15504,18 +15459,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J15" s="89">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="3:11" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="83" t="s">
         <v>275</v>
       </c>
@@ -15538,7 +15493,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
@@ -15559,7 +15514,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
@@ -15580,7 +15535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D21" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
@@ -15601,7 +15556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
@@ -15622,7 +15577,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
@@ -15643,7 +15598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
@@ -15664,18 +15619,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J26" s="89">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D27" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="29" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="83" t="s">
         <v>275</v>
       </c>
@@ -15698,7 +15653,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="str">
         <f>"Livestock production region"</f>
         <v>Livestock production region</v>
@@ -15719,7 +15674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="str">
         <f>"Cattle breed"</f>
         <v>Cattle breed</v>
@@ -15740,7 +15695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="str">
         <f>"Head count"</f>
         <v>Head count</v>
@@ -15761,7 +15716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="str">
         <f>"Liveweight"</f>
         <v>Liveweight</v>
@@ -15782,7 +15737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D34" s="1" t="str">
         <f>"Liveweight gain"</f>
         <v>Liveweight gain</v>
@@ -15803,7 +15758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="1" t="str">
         <f>"Dry matter digestibility of diet"</f>
         <v>Dry matter digestibility of diet</v>
@@ -15824,7 +15779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="1" t="str">
         <f>"Crude protein in diet"</f>
         <v>Crude protein in diet</v>
@@ -15845,7 +15800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="1" t="str">
         <f>"Livestock access to water bodies"</f>
         <v>Livestock access to water bodies</v>
@@ -15866,7 +15821,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D38" s="1" t="str">
         <f>"Calving timing"</f>
         <v>Calving timing</v>
@@ -15887,7 +15842,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D39" s="1" t="str">
         <f>"Calving rates"</f>
         <v>Calving rates</v>
@@ -15908,7 +15863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D40" s="1" t="str">
         <f>"Livestock sales"</f>
         <v>Livestock sales</v>
@@ -15929,7 +15884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="1" t="str">
         <f>"Livestock purchases"</f>
         <v>Livestock purchases</v>
@@ -15950,18 +15905,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J43" s="89">
         <f>SUM(Table_Input_DataQuality_PastureBeef[Score])</f>
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D44" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="83" t="s">
         <v>275</v>
       </c>
@@ -15984,7 +15939,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="str">
         <f>"Pasture type"</f>
         <v>Pasture type</v>
@@ -16005,7 +15960,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="str">
         <f>"Irrigation method"</f>
         <v>Irrigation method</v>
@@ -16026,7 +15981,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="str">
         <f>"Area under pasture"</f>
         <v>Area under pasture</v>
@@ -16047,7 +16002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="1" t="str">
         <f>"Pasture yield"</f>
         <v>Pasture yield</v>
@@ -16068,7 +16023,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="str">
         <f>"Area of pasture renewed or removed"</f>
         <v>Area of pasture renewed or removed</v>
@@ -16089,18 +16044,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J53" s="89">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>64</v>
       </c>
     </row>
-    <row r="54" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D54" s="2" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="83" t="s">
         <v>275</v>
       </c>
@@ -16123,7 +16078,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="1" t="str">
         <f>"Branded inorganic fertiliser applications"</f>
         <v>Branded inorganic fertiliser applications</v>
@@ -16144,7 +16099,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="str">
         <f>"Custom inorganic fertiliser blend applications"</f>
         <v>Custom inorganic fertiliser blend applications</v>
@@ -16165,7 +16120,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="1" t="str">
         <f>"Lime applications"</f>
         <v>Lime applications</v>
@@ -16186,7 +16141,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D60" s="1" t="str">
         <f>"Organic fertiliser applications"</f>
         <v>Organic fertiliser applications</v>
@@ -16207,18 +16162,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J62" s="89">
         <f>SUM(Table_Input_DataQuality_FertiliserApplications[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D63" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="65" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D65" s="83" t="s">
         <v>275</v>
       </c>
@@ -16241,7 +16196,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D66" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
@@ -16262,7 +16217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
@@ -16283,7 +16238,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D68" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
@@ -16304,7 +16259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D69" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
@@ -16325,18 +16280,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J71" s="89">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="73" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D73" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="75" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D75" s="83" t="s">
         <v>275</v>
       </c>
@@ -16359,7 +16314,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="76" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D76" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
@@ -16380,7 +16335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D77" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
@@ -16401,7 +16356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
@@ -16422,7 +16377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D79" s="1" t="str">
         <f>"Use of contractors and service providers"</f>
         <v>Use of contractors and service providers</v>
@@ -16437,7 +16392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D80" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
@@ -16458,13 +16413,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J82" s="89">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D84" s="92" t="s">
         <v>278</v>
       </c>
@@ -16504,7 +16459,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="23" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="23" customWidth="1"/>
@@ -16537,10 +16492,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -16567,11 +16522,11 @@
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="26"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -16579,7 +16534,7 @@
       </c>
       <c r="BM5" s="26"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="87" t="s">
         <v>2</v>
       </c>
@@ -16593,7 +16548,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="88" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -16611,7 +16566,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -16629,7 +16584,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="21" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16644,7 +16599,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="21" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16659,7 +16614,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="21" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16675,7 +16630,7 @@
       </c>
       <c r="BM11" s="26"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="21" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16691,7 +16646,7 @@
       </c>
       <c r="BM12" s="26"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="21" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16706,7 +16661,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="21" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16721,129 +16676,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="21" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="21" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="21" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="21" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="21" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="21" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="21" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="21" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="21" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="21" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="21" t="s">
         <v>35</v>
@@ -16852,7 +16807,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="21" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16863,7 +16818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="21" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16874,7 +16829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="21" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16885,7 +16840,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="21" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16896,7 +16851,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="21" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16907,7 +16862,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="21" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16918,7 +16873,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="21" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16929,24 +16884,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="21" t="s">
         <v>35</v>
@@ -16964,7 +16919,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="21" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -16987,7 +16942,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="21" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17010,7 +16965,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="21" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17033,7 +16988,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="21" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17056,7 +17011,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="21" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17079,7 +17034,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="21" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17102,7 +17057,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="21" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17125,49 +17080,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="27" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="27" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="21" t="s">
         <v>41</v>
@@ -17176,7 +17131,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="21" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17187,7 +17142,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="21" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17198,7 +17153,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="21" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17209,7 +17164,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="21" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17220,7 +17175,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="21" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17231,7 +17186,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="21" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17242,7 +17197,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="21" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17253,7 +17208,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="21" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17264,7 +17219,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="21" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17275,7 +17230,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="21" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17286,7 +17241,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="21" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17297,7 +17252,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="21" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17308,7 +17263,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="21" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17319,7 +17274,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="21" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17330,64 +17285,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="27" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="27" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="27" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="27" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="21" t="s">
         <v>41</v>
@@ -17439,7 +17394,7 @@
       </c>
       <c r="T89" s="21"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="21" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17507,7 +17462,7 @@
       </c>
       <c r="T90" s="21"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="21" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17575,7 +17530,7 @@
       </c>
       <c r="T91" s="21"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="21" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17643,7 +17598,7 @@
       </c>
       <c r="T92" s="21"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="21" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17711,7 +17666,7 @@
       </c>
       <c r="T93" s="21"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="21" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17779,7 +17734,7 @@
       </c>
       <c r="T94" s="21"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="21" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17847,7 +17802,7 @@
       </c>
       <c r="T95" s="21"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="21" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17915,7 +17870,7 @@
       </c>
       <c r="T96" s="21"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="21" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17983,66 +17938,66 @@
       </c>
       <c r="T97" s="21"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="27" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="21" t="s">
         <v>58</v>
@@ -18057,7 +18012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="21" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18076,7 +18031,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="21" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18095,7 +18050,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="21" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18114,13 +18069,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18128,7 +18083,7 @@
       </c>
       <c r="BN115" s="23"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18136,7 +18091,7 @@
       </c>
       <c r="BN116" s="23"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="27" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18144,11 +18099,11 @@
       </c>
       <c r="BN117" s="23"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="23"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="21" t="s">
         <v>61</v>
@@ -18164,7 +18119,7 @@
       </c>
       <c r="BN119" s="23"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="21" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18184,7 +18139,7 @@
       </c>
       <c r="BN120" s="23"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="21" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18204,31 +18159,31 @@
       </c>
       <c r="BN121" s="23"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="23"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="21" t="s">
         <v>63</v>
@@ -18237,7 +18192,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="21" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18248,7 +18203,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="21" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18259,13 +18214,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18273,7 +18228,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18281,7 +18236,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>65</v>
@@ -18290,7 +18245,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18301,7 +18256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18312,10 +18267,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="23"/>
       <c r="BO138" s="23"/>
@@ -18330,7 +18285,7 @@
       <c r="BX138" s="23"/>
       <c r="BY138" s="23"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18349,7 +18304,7 @@
       <c r="BX139" s="23"/>
       <c r="BY139" s="23"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18368,7 +18323,7 @@
       <c r="BX140" s="23"/>
       <c r="BY140" s="23"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="27" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18376,7 +18331,7 @@
       </c>
       <c r="BN141" s="23"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="21" t="s">
         <v>67</v>
@@ -18386,7 +18341,7 @@
       </c>
       <c r="BN142" s="23"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="21" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18398,7 +18353,7 @@
       </c>
       <c r="BN143" s="23"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18410,7 +18365,7 @@
       </c>
       <c r="BN144" s="23"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18422,7 +18377,7 @@
       </c>
       <c r="BN145" s="23"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18434,7 +18389,7 @@
       </c>
       <c r="BN146" s="23"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18446,15 +18401,15 @@
       </c>
       <c r="BN147" s="23"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="23"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="23"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18462,7 +18417,7 @@
       </c>
       <c r="BN150" s="23"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18470,11 +18425,11 @@
       </c>
       <c r="BN151" s="23"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="23"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="21" t="s">
         <v>68</v>
@@ -18494,7 +18449,7 @@
       <c r="BL153" s="26"/>
       <c r="BM153" s="26"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="21" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18516,7 +18471,7 @@
       <c r="BL154" s="26"/>
       <c r="BM154" s="26"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="21" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18538,7 +18493,7 @@
       <c r="BL155" s="26"/>
       <c r="BM155" s="26"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="21" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18549,7 +18504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="21" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18560,7 +18515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="21" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18571,34 +18526,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -18607,17 +18562,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="23"/>
       <c r="BO165" s="23"/>
       <c r="BP165" s="23"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="23"/>
       <c r="BO166" s="23"/>
       <c r="BP166" s="23"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -18626,7 +18581,7 @@
       <c r="BO167" s="23"/>
       <c r="BP167" s="23"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -18635,7 +18590,7 @@
       <c r="BO168" s="23"/>
       <c r="BP168" s="23"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -18644,7 +18599,7 @@
       <c r="BO169" s="23"/>
       <c r="BP169" s="23"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -18656,17 +18611,17 @@
       <c r="BO170" s="23"/>
       <c r="BP170" s="23"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="23"/>
       <c r="BO171" s="23"/>
       <c r="BP171" s="23"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="23"/>
       <c r="BO172" s="23"/>
       <c r="BP172" s="23"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -18675,7 +18630,7 @@
       <c r="BO173" s="23"/>
       <c r="BP173" s="23"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -18684,7 +18639,7 @@
       <c r="BO174" s="23"/>
       <c r="BP174" s="23"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -18697,17 +18652,17 @@
       <c r="BO175" s="23"/>
       <c r="BP175" s="23"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="23"/>
       <c r="BO176" s="23"/>
       <c r="BP176" s="23"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="23"/>
       <c r="BO177" s="23"/>
       <c r="BP177" s="23"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -18716,7 +18671,7 @@
       <c r="BO178" s="23"/>
       <c r="BP178" s="23"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -18725,39 +18680,39 @@
       <c r="BO179" s="23"/>
       <c r="BP179" s="23"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="27" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="27" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="27" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="27" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="27" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="21" t="s">
         <v>70</v>
       </c>
@@ -18774,7 +18729,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="21" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -18796,7 +18751,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="21" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -18818,7 +18773,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="21" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18840,7 +18795,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="21" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18862,7 +18817,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="21" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -18884,7 +18839,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="21" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -18906,7 +18861,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="21" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -18928,7 +18883,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="21" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -18950,7 +18905,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="21" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -18972,7 +18927,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="21" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -18994,7 +18949,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="21" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19016,7 +18971,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="21" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19038,7 +18993,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="21" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19060,31 +19015,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="27" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="21" t="s">
         <v>41</v>
       </c>
@@ -19092,7 +19047,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="21" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19102,7 +19057,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19112,13 +19067,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="21" t="s">
         <v>76</v>
       </c>
@@ -19126,7 +19081,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="21" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19136,7 +19091,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19146,7 +19101,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19156,7 +19111,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19166,7 +19121,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19176,7 +19131,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19186,7 +19141,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19196,7 +19151,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19206,7 +19161,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19216,7 +19171,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19226,7 +19181,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19236,7 +19191,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19246,25 +19201,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="27" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="21" t="s">
         <v>78</v>
       </c>
@@ -19314,7 +19269,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="21" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19380,7 +19335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19446,7 +19401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19512,7 +19467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19578,7 +19533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19644,7 +19599,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19710,7 +19665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19776,7 +19731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19842,7 +19797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19908,7 +19863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19974,7 +19929,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20040,7 +19995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20106,7 +20061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20172,7 +20127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20238,7 +20193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20304,7 +20259,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20370,7 +20325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20436,7 +20391,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20502,7 +20457,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20568,31 +20523,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="21" t="s">
         <v>94</v>
       </c>
@@ -20600,7 +20555,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="21" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -20610,7 +20565,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -20620,17 +20575,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="21" t="s">
         <v>269</v>
       </c>
@@ -20646,7 +20601,7 @@
       <c r="V265" s="1"/>
       <c r="BN265" s="23"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="21" t="s">
         <v>250</v>
       </c>
@@ -20662,7 +20617,7 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="23"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="21" t="s">
         <v>257</v>
       </c>
@@ -20678,7 +20633,7 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="23"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="21" t="s">
         <v>258</v>
       </c>
@@ -20694,7 +20649,7 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="23"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="21" t="s">
         <v>267</v>
       </c>
@@ -20710,7 +20665,7 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="23"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="21" t="s">
         <v>268</v>
       </c>
@@ -20726,12 +20681,12 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="23"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="21" t="s">
         <v>269</v>
       </c>
@@ -20747,7 +20702,7 @@
       <c r="V274" s="1"/>
       <c r="BN274" s="23"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="21" t="s">
         <v>265</v>
       </c>
@@ -20763,7 +20718,7 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="23"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="21" t="s">
         <v>251</v>
       </c>
@@ -20779,7 +20734,7 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="23"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="21" t="s">
         <v>254</v>
       </c>
@@ -20795,7 +20750,7 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="23"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="21" t="s">
         <v>263</v>
       </c>
@@ -20811,7 +20766,7 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="23"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="21" t="s">
         <v>266</v>
       </c>
@@ -20827,12 +20782,12 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="23"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="21" t="s">
         <v>269</v>
       </c>
@@ -20848,7 +20803,7 @@
       <c r="V283" s="1"/>
       <c r="BN283" s="23"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="21" t="s">
         <v>252</v>
       </c>
@@ -20864,7 +20819,7 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="23"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="21" t="s">
         <v>255</v>
       </c>
@@ -20880,7 +20835,7 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="23"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="21" t="s">
         <v>253</v>
       </c>
@@ -20896,7 +20851,7 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="23"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="21" t="s">
         <v>260</v>
       </c>
@@ -20912,7 +20867,7 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="23"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="21" t="s">
         <v>261</v>
       </c>
@@ -20928,12 +20883,12 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="23"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="21" t="s">
         <v>269</v>
       </c>
@@ -20949,7 +20904,7 @@
       <c r="V292" s="1"/>
       <c r="BN292" s="23"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="21" t="s">
         <v>270</v>
       </c>
@@ -20965,7 +20920,7 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="23"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="21" t="s">
         <v>271</v>
       </c>
@@ -20981,7 +20936,7 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="23"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="21" t="s">
         <v>272</v>
       </c>
@@ -20997,7 +20952,7 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="23"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="21" t="s">
         <v>273</v>
       </c>
@@ -21013,7 +20968,7 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="23"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="21" t="s">
         <v>274</v>
       </c>
